--- a/Дозор_Пеленг/MB_856/РАСПИНОВКА_856.xlsx
+++ b/Дозор_Пеленг/MB_856/РАСПИНОВКА_856.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20384"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VPL\DOZOR\PCB_856\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agest\Downloads\Telegram Desktop\Дозор_Пеленг\MB_856\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAAE894A-950F-446A-ADC4-C7F0A0867DDF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="5835"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
   <si>
     <t>P0.0</t>
   </si>
@@ -207,12 +208,18 @@
   </si>
   <si>
     <t>PH21</t>
+  </si>
+  <si>
+    <t>VINR</t>
+  </si>
+  <si>
+    <t>LED</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -562,14 +569,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
@@ -590,12 +597,12 @@
       </c>
       <c r="I1" s="11"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="10">
@@ -617,12 +624,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="10">
@@ -644,7 +651,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -671,7 +678,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -686,7 +693,7 @@
       <c r="H5" s="6"/>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -701,7 +708,7 @@
       <c r="H6" s="8"/>
       <c r="I6" s="7"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -716,7 +723,7 @@
       <c r="H7" s="8"/>
       <c r="I7" s="7"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -731,7 +738,7 @@
       <c r="H8" s="6"/>
       <c r="I8" s="7"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -746,7 +753,7 @@
       <c r="H9" s="8"/>
       <c r="I9" s="7"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="4"/>
       <c r="C10" s="3"/>
@@ -757,7 +764,7 @@
       <c r="H10" s="8"/>
       <c r="I10" s="7"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
@@ -768,14 +775,14 @@
       <c r="D11" s="5"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="4"/>
       <c r="C12" s="2"/>
       <c r="D12" s="5"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
@@ -786,7 +793,7 @@
       <c r="D13" s="5"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
@@ -797,7 +804,7 @@
       <c r="D14" s="5"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -808,7 +815,7 @@
       <c r="D15" s="5"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
@@ -819,7 +826,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
@@ -830,7 +837,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
@@ -841,7 +848,7 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -852,7 +859,7 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>15</v>
       </c>
@@ -863,14 +870,14 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="4"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>16</v>
       </c>
@@ -881,7 +888,7 @@
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>17</v>
       </c>
@@ -892,7 +899,7 @@
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>18</v>
       </c>
@@ -903,7 +910,7 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -914,7 +921,7 @@
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>20</v>
       </c>
@@ -925,7 +932,7 @@
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>21</v>
       </c>
@@ -936,7 +943,7 @@
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>22</v>
       </c>
@@ -947,7 +954,7 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>23</v>
       </c>
@@ -958,42 +965,42 @@
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="4"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="4"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
